--- a/excel/robotUpgrade.xlsx
+++ b/excel/robotUpgrade.xlsx
@@ -1145,10 +1145,10 @@
         <v>12</v>
       </c>
       <c r="C6" s="4">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1159,10 +1159,10 @@
         <v>13</v>
       </c>
       <c r="C7" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1173,10 +1173,10 @@
         <v>12</v>
       </c>
       <c r="C8" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D8" s="4">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1187,10 +1187,10 @@
         <v>12</v>
       </c>
       <c r="C9" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D9" s="4">
-        <v>45</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1201,10 +1201,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="4">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D10" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1215,7 +1215,7 @@
         <v>13</v>
       </c>
       <c r="C11" s="4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D11" s="4">
         <v>20</v>
@@ -1229,10 +1229,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1271,10 +1271,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="4">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D15" s="4">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1285,10 +1285,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="4">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D16" s="4">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1299,7 +1299,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="4">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D17" s="4">
         <v>60</v>
@@ -1313,7 +1313,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D18" s="4">
         <v>50</v>

--- a/excel/robotUpgrade.xlsx
+++ b/excel/robotUpgrade.xlsx
@@ -1145,10 +1145,10 @@
         <v>12</v>
       </c>
       <c r="C6" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D6" s="4">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1162,7 +1162,7 @@
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1173,10 +1173,10 @@
         <v>12</v>
       </c>
       <c r="C8" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1201,10 +1201,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D10" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1215,10 +1215,10 @@
         <v>13</v>
       </c>
       <c r="C11" s="4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D11" s="4">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1229,10 +1229,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1257,10 +1257,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D14" s="4">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1271,7 +1271,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="4">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D15" s="4">
         <v>60</v>
@@ -1285,10 +1285,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="4">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D16" s="4">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1299,10 +1299,10 @@
         <v>13</v>
       </c>
       <c r="C17" s="4">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D17" s="4">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1327,7 +1327,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="4">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D19" s="4">
         <v>90</v>
@@ -1341,10 +1341,10 @@
         <v>12</v>
       </c>
       <c r="C20" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D20" s="4">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1355,10 +1355,10 @@
         <v>13</v>
       </c>
       <c r="C21" s="4">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="D21" s="4">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1369,10 +1369,10 @@
         <v>12</v>
       </c>
       <c r="C22" s="4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D22" s="4">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1383,10 +1383,10 @@
         <v>13</v>
       </c>
       <c r="C23" s="4">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D23" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1397,10 +1397,10 @@
         <v>12</v>
       </c>
       <c r="C24" s="4">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D24" s="4">
-        <v>45</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1411,10 +1411,10 @@
         <v>13</v>
       </c>
       <c r="C25" s="4">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D25" s="4">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:4">

--- a/excel/robotUpgrade.xlsx
+++ b/excel/robotUpgrade.xlsx
@@ -1187,10 +1187,10 @@
         <v>12</v>
       </c>
       <c r="C9" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D9" s="4">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1201,10 +1201,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D10" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1215,10 +1215,10 @@
         <v>13</v>
       </c>
       <c r="C11" s="4">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D11" s="4">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1229,10 +1229,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D12" s="4">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1271,10 +1271,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D15" s="4">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1285,10 +1285,10 @@
         <v>13</v>
       </c>
       <c r="C16" s="4">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D16" s="4">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1299,10 +1299,10 @@
         <v>13</v>
       </c>
       <c r="C17" s="4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D17" s="4">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1313,10 +1313,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D18" s="4">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1327,10 +1327,10 @@
         <v>13</v>
       </c>
       <c r="C19" s="4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D19" s="4">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1355,10 +1355,10 @@
         <v>13</v>
       </c>
       <c r="C21" s="4">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D21" s="4">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1383,10 +1383,10 @@
         <v>13</v>
       </c>
       <c r="C23" s="4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D23" s="4">
-        <v>120</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1411,10 +1411,10 @@
         <v>13</v>
       </c>
       <c r="C25" s="4">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D25" s="4">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:4">

--- a/excel/robotUpgrade.xlsx
+++ b/excel/robotUpgrade.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameSVN\game002\cocosProject\LieFlatGame\excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -1128,10 +1123,10 @@
         <v>10</v>
       </c>
       <c r="C6" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1142,10 +1137,10 @@
         <v>10</v>
       </c>
       <c r="C7" s="3">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1198,7 +1193,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D11" s="3">
         <v>45</v>

--- a/excel/robotUpgrade.xlsx
+++ b/excel/robotUpgrade.xlsx
@@ -1123,7 +1123,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D6" s="3">
         <v>30</v>
@@ -1137,7 +1137,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D7" s="3">
         <v>35</v>
